--- a/research/traditional_assets/database/data/belgium/belgium_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_insurance_general.xlsx
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00351</v>
+        <v>-0.0428</v>
       </c>
       <c r="E2">
-        <v>0.199</v>
+        <v>0.296</v>
       </c>
       <c r="F2">
-        <v>-0.0506</v>
+        <v>0.138</v>
       </c>
       <c r="G2">
-        <v>0.1369938131826305</v>
+        <v>0.179713679636822</v>
       </c>
       <c r="H2">
-        <v>0.1369938131826305</v>
+        <v>0.179713679636822</v>
       </c>
       <c r="I2">
-        <v>0.06848077828743218</v>
+        <v>0.1554881485504647</v>
       </c>
       <c r="J2">
-        <v>0.05547906332846568</v>
+        <v>0.1296964345221413</v>
       </c>
       <c r="K2">
-        <v>828.8</v>
+        <v>962.5</v>
       </c>
       <c r="L2">
-        <v>0.05346855303308883</v>
+        <v>0.09863398337825237</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2590.4</v>
+        <v>1672.2</v>
       </c>
       <c r="V2">
-        <v>0.2687443587961282</v>
+        <v>0.2043929448865095</v>
       </c>
       <c r="W2">
-        <v>0.0627299011519656</v>
+        <v>0.0720062243302486</v>
       </c>
       <c r="X2">
-        <v>0.0681754844218205</v>
+        <v>0.1073571776046811</v>
       </c>
       <c r="Y2">
-        <v>-0.005445583269854906</v>
+        <v>-0.03535095327443251</v>
       </c>
       <c r="Z2">
-        <v>0.8922036434800127</v>
+        <v>0.5249389436990973</v>
       </c>
       <c r="AA2">
-        <v>0.04949862243851544</v>
+        <v>0.068082709339592</v>
       </c>
       <c r="AB2">
-        <v>0.04791216769269421</v>
+        <v>0.0788060562306879</v>
       </c>
       <c r="AC2">
-        <v>0.001586454745821225</v>
+        <v>-0.0107233468910959</v>
       </c>
       <c r="AD2">
-        <v>7812.9</v>
+        <v>6677.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7812.9</v>
+        <v>6677.6</v>
       </c>
       <c r="AG2">
-        <v>5222.5</v>
+        <v>5005.400000000001</v>
       </c>
       <c r="AH2">
-        <v>0.4476844795379273</v>
+        <v>0.4494006958792374</v>
       </c>
       <c r="AI2">
-        <v>0.3291402139249198</v>
+        <v>0.4317097454065866</v>
       </c>
       <c r="AJ2">
-        <v>0.3514137295275008</v>
+        <v>0.3795794247233956</v>
       </c>
       <c r="AK2">
-        <v>0.2469629118215909</v>
+        <v>0.362825828525037</v>
       </c>
       <c r="AL2">
-        <v>135.7</v>
+        <v>148.4</v>
       </c>
       <c r="AM2">
-        <v>135.7</v>
+        <v>148.4</v>
       </c>
       <c r="AN2">
-        <v>5.947700974421437</v>
+        <v>3.672441291316065</v>
       </c>
       <c r="AO2">
-        <v>7.822402358142963</v>
+        <v>10.2243935309973</v>
       </c>
       <c r="AP2">
-        <v>3.975715590742996</v>
+        <v>2.752791068580543</v>
       </c>
       <c r="AQ2">
-        <v>7.822402358142963</v>
+        <v>10.2243935309973</v>
       </c>
     </row>
     <row r="3">
@@ -722,31 +722,31 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00351</v>
+        <v>-0.0428</v>
       </c>
       <c r="E3">
-        <v>0.199</v>
+        <v>0.296</v>
       </c>
       <c r="F3">
-        <v>-0.0506</v>
+        <v>0.138</v>
       </c>
       <c r="G3">
-        <v>0.1369938131826305</v>
+        <v>0.179713679636822</v>
       </c>
       <c r="H3">
-        <v>0.1369938131826305</v>
+        <v>0.179713679636822</v>
       </c>
       <c r="I3">
-        <v>0.06848077828743218</v>
+        <v>0.1554881485504647</v>
       </c>
       <c r="J3">
-        <v>0.05547906332846568</v>
+        <v>0.1296964345221413</v>
       </c>
       <c r="K3">
-        <v>828.8</v>
+        <v>962.5</v>
       </c>
       <c r="L3">
-        <v>0.05346855303308883</v>
+        <v>0.09863398337825237</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2590.4</v>
+        <v>1672.2</v>
       </c>
       <c r="V3">
-        <v>0.2687443587961282</v>
+        <v>0.2043929448865095</v>
       </c>
       <c r="W3">
-        <v>0.0627299011519656</v>
+        <v>0.0720062243302486</v>
       </c>
       <c r="X3">
-        <v>0.0681754844218205</v>
+        <v>0.1073571776046811</v>
       </c>
       <c r="Y3">
-        <v>-0.005445583269854906</v>
+        <v>-0.03535095327443251</v>
       </c>
       <c r="Z3">
-        <v>0.8922036434800127</v>
+        <v>0.5249389436990973</v>
       </c>
       <c r="AA3">
-        <v>0.04949862243851544</v>
+        <v>0.068082709339592</v>
       </c>
       <c r="AB3">
-        <v>0.04791216769269421</v>
+        <v>0.0788060562306879</v>
       </c>
       <c r="AC3">
-        <v>0.001586454745821225</v>
+        <v>-0.0107233468910959</v>
       </c>
       <c r="AD3">
-        <v>7812.9</v>
+        <v>6677.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7812.9</v>
+        <v>6677.6</v>
       </c>
       <c r="AG3">
-        <v>5222.5</v>
+        <v>5005.400000000001</v>
       </c>
       <c r="AH3">
-        <v>0.4476844795379273</v>
+        <v>0.4494006958792374</v>
       </c>
       <c r="AI3">
-        <v>0.3291402139249198</v>
+        <v>0.4317097454065866</v>
       </c>
       <c r="AJ3">
-        <v>0.3514137295275008</v>
+        <v>0.3795794247233956</v>
       </c>
       <c r="AK3">
-        <v>0.2469629118215909</v>
+        <v>0.362825828525037</v>
       </c>
       <c r="AL3">
-        <v>135.7</v>
+        <v>148.4</v>
       </c>
       <c r="AM3">
-        <v>135.7</v>
+        <v>148.4</v>
       </c>
       <c r="AN3">
-        <v>5.947700974421437</v>
+        <v>3.672441291316065</v>
       </c>
       <c r="AO3">
-        <v>7.822402358142963</v>
+        <v>10.2243935309973</v>
       </c>
       <c r="AP3">
-        <v>3.975715590742996</v>
+        <v>2.752791068580543</v>
       </c>
       <c r="AQ3">
-        <v>7.822402358142963</v>
+        <v>10.2243935309973</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/belgium/belgium_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_insurance_general.xlsx
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0428</v>
+        <v>0.00062</v>
       </c>
       <c r="E2">
-        <v>0.296</v>
+        <v>0.0313</v>
       </c>
       <c r="F2">
-        <v>0.138</v>
+        <v>0.146</v>
       </c>
       <c r="G2">
-        <v>0.179713679636822</v>
+        <v>0.1441515893863818</v>
       </c>
       <c r="H2">
-        <v>0.179713679636822</v>
+        <v>0.1441515893863818</v>
       </c>
       <c r="I2">
-        <v>0.1554881485504647</v>
+        <v>0.3086021664059503</v>
       </c>
       <c r="J2">
-        <v>0.1296964345221413</v>
+        <v>0.2520869274723158</v>
       </c>
       <c r="K2">
-        <v>962.5</v>
+        <v>994.5</v>
       </c>
       <c r="L2">
-        <v>0.09863398337825237</v>
+        <v>0.07338183642749624</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>600.4</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.07523809523809523</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.6037204625439919</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>589.5</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.07387218045112783</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.5927601809954751</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>10.89999999999998</v>
+      </c>
+      <c r="T2">
+        <v>0.01815456362425046</v>
       </c>
       <c r="U2">
-        <v>1672.2</v>
+        <v>1651.7</v>
       </c>
       <c r="V2">
-        <v>0.2043929448865095</v>
+        <v>0.2069799498746867</v>
       </c>
       <c r="W2">
-        <v>0.0720062243302486</v>
+        <v>0.1054579387718312</v>
       </c>
       <c r="X2">
-        <v>0.1073571776046811</v>
+        <v>0.09753636610495922</v>
       </c>
       <c r="Y2">
-        <v>-0.03535095327443251</v>
+        <v>0.007921572666872018</v>
       </c>
       <c r="Z2">
-        <v>0.5249389436990973</v>
+        <v>0.8649124710417319</v>
       </c>
       <c r="AA2">
-        <v>0.068082709339592</v>
+        <v>0.2180331273573984</v>
       </c>
       <c r="AB2">
-        <v>0.0788060562306879</v>
+        <v>0.06974757697227713</v>
       </c>
       <c r="AC2">
-        <v>-0.0107233468910959</v>
+        <v>0.1482855503851213</v>
       </c>
       <c r="AD2">
-        <v>6677.6</v>
+        <v>7692.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6677.6</v>
+        <v>7692.1</v>
       </c>
       <c r="AG2">
-        <v>5005.400000000001</v>
+        <v>6040.400000000001</v>
       </c>
       <c r="AH2">
-        <v>0.4494006958792374</v>
+        <v>0.4908148876028101</v>
       </c>
       <c r="AI2">
-        <v>0.4317097454065866</v>
+        <v>0.4620323874966963</v>
       </c>
       <c r="AJ2">
-        <v>0.3795794247233956</v>
+        <v>0.4308293629283045</v>
       </c>
       <c r="AK2">
-        <v>0.362825828525037</v>
+        <v>0.4027819453613128</v>
       </c>
       <c r="AL2">
-        <v>148.4</v>
+        <v>193.2</v>
       </c>
       <c r="AM2">
-        <v>148.4</v>
+        <v>193.2</v>
       </c>
       <c r="AN2">
-        <v>3.672441291316065</v>
+        <v>1.681223089196337</v>
       </c>
       <c r="AO2">
-        <v>10.2243935309973</v>
+        <v>21.64751552795031</v>
       </c>
       <c r="AP2">
-        <v>2.752791068580543</v>
+        <v>1.320219439162459</v>
       </c>
       <c r="AQ2">
-        <v>10.2243935309973</v>
+        <v>21.64751552795031</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0428</v>
+        <v>0.00062</v>
       </c>
       <c r="E3">
-        <v>0.296</v>
+        <v>0.0313</v>
       </c>
       <c r="F3">
-        <v>0.138</v>
+        <v>0.146</v>
       </c>
       <c r="G3">
-        <v>0.179713679636822</v>
+        <v>0.1441515893863818</v>
       </c>
       <c r="H3">
-        <v>0.179713679636822</v>
+        <v>0.1441515893863818</v>
       </c>
       <c r="I3">
-        <v>0.1554881485504647</v>
+        <v>0.3086021664059503</v>
       </c>
       <c r="J3">
-        <v>0.1296964345221413</v>
+        <v>0.2520869274723158</v>
       </c>
       <c r="K3">
-        <v>962.5</v>
+        <v>994.5</v>
       </c>
       <c r="L3">
-        <v>0.09863398337825237</v>
+        <v>0.07338183642749624</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>600.4</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.07523809523809523</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.6037204625439919</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>589.5</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.07387218045112783</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.5927601809954751</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>10.89999999999998</v>
+      </c>
+      <c r="T3">
+        <v>0.01815456362425046</v>
       </c>
       <c r="U3">
-        <v>1672.2</v>
+        <v>1651.7</v>
       </c>
       <c r="V3">
-        <v>0.2043929448865095</v>
+        <v>0.2069799498746867</v>
       </c>
       <c r="W3">
-        <v>0.0720062243302486</v>
+        <v>0.1054579387718312</v>
       </c>
       <c r="X3">
-        <v>0.1073571776046811</v>
+        <v>0.09753636610495922</v>
       </c>
       <c r="Y3">
-        <v>-0.03535095327443251</v>
+        <v>0.007921572666872018</v>
       </c>
       <c r="Z3">
-        <v>0.5249389436990973</v>
+        <v>0.8649124710417319</v>
       </c>
       <c r="AA3">
-        <v>0.068082709339592</v>
+        <v>0.2180331273573984</v>
       </c>
       <c r="AB3">
-        <v>0.0788060562306879</v>
+        <v>0.06974757697227713</v>
       </c>
       <c r="AC3">
-        <v>-0.0107233468910959</v>
+        <v>0.1482855503851213</v>
       </c>
       <c r="AD3">
-        <v>6677.6</v>
+        <v>7692.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6677.6</v>
+        <v>7692.1</v>
       </c>
       <c r="AG3">
-        <v>5005.400000000001</v>
+        <v>6040.400000000001</v>
       </c>
       <c r="AH3">
-        <v>0.4494006958792374</v>
+        <v>0.4908148876028101</v>
       </c>
       <c r="AI3">
-        <v>0.4317097454065866</v>
+        <v>0.4620323874966963</v>
       </c>
       <c r="AJ3">
-        <v>0.3795794247233956</v>
+        <v>0.4308293629283045</v>
       </c>
       <c r="AK3">
-        <v>0.362825828525037</v>
+        <v>0.4027819453613128</v>
       </c>
       <c r="AL3">
-        <v>148.4</v>
+        <v>193.2</v>
       </c>
       <c r="AM3">
-        <v>148.4</v>
+        <v>193.2</v>
       </c>
       <c r="AN3">
-        <v>3.672441291316065</v>
+        <v>1.681223089196337</v>
       </c>
       <c r="AO3">
-        <v>10.2243935309973</v>
+        <v>21.64751552795031</v>
       </c>
       <c r="AP3">
-        <v>2.752791068580543</v>
+        <v>1.320219439162459</v>
       </c>
       <c r="AQ3">
-        <v>10.2243935309973</v>
+        <v>21.64751552795031</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/belgium/belgium_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00062</v>
+        <v>-0.09820000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0313</v>
+        <v>0.0179</v>
       </c>
       <c r="F2">
-        <v>0.146</v>
+        <v>0.165</v>
       </c>
       <c r="G2">
-        <v>0.1441515893863818</v>
+        <v>0.1607987569776141</v>
       </c>
       <c r="H2">
-        <v>0.1441515893863818</v>
+        <v>0.1607987569776141</v>
       </c>
       <c r="I2">
-        <v>0.3086021664059503</v>
+        <v>0.1197444898428958</v>
       </c>
       <c r="J2">
-        <v>0.2520869274723158</v>
+        <v>0.1006980860497364</v>
       </c>
       <c r="K2">
-        <v>994.5</v>
+        <v>1140</v>
       </c>
       <c r="L2">
-        <v>0.07338183642749624</v>
+        <v>0.1312079185129769</v>
       </c>
       <c r="M2">
-        <v>600.4</v>
+        <v>626.8</v>
       </c>
       <c r="N2">
-        <v>0.07523809523809523</v>
+        <v>0.07028245293385511</v>
       </c>
       <c r="O2">
-        <v>0.6037204625439919</v>
+        <v>0.5498245614035088</v>
       </c>
       <c r="P2">
-        <v>589.5</v>
+        <v>626.8</v>
       </c>
       <c r="Q2">
-        <v>0.07387218045112783</v>
+        <v>0.07028245293385511</v>
       </c>
       <c r="R2">
-        <v>0.5927601809954751</v>
+        <v>0.5498245614035088</v>
       </c>
       <c r="S2">
-        <v>10.89999999999998</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.01815456362425046</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1651.7</v>
+        <v>2395.8</v>
       </c>
       <c r="V2">
-        <v>0.2069799498746867</v>
+        <v>0.2686386418936345</v>
       </c>
       <c r="W2">
-        <v>0.1054579387718312</v>
+        <v>0.1445306557127643</v>
       </c>
       <c r="X2">
-        <v>0.09753636610495922</v>
+        <v>0.09723750162383599</v>
       </c>
       <c r="Y2">
-        <v>0.007921572666872018</v>
+        <v>0.04729315408892834</v>
       </c>
       <c r="Z2">
-        <v>0.8649124710417319</v>
+        <v>0.6238153360137851</v>
       </c>
       <c r="AA2">
-        <v>0.2180331273573984</v>
+        <v>0.06281701038506134</v>
       </c>
       <c r="AB2">
-        <v>0.06974757697227713</v>
+        <v>0.07361927331655713</v>
       </c>
       <c r="AC2">
-        <v>0.1482855503851213</v>
+        <v>-0.01080226293149579</v>
       </c>
       <c r="AD2">
-        <v>7692.1</v>
+        <v>7252.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7692.1</v>
+        <v>7252.8</v>
       </c>
       <c r="AG2">
-        <v>6040.400000000001</v>
+        <v>4857</v>
       </c>
       <c r="AH2">
-        <v>0.4908148876028101</v>
+        <v>0.4485038123566115</v>
       </c>
       <c r="AI2">
-        <v>0.4620323874966963</v>
+        <v>0.4421010283262117</v>
       </c>
       <c r="AJ2">
-        <v>0.4308293629283045</v>
+        <v>0.3525876024478596</v>
       </c>
       <c r="AK2">
-        <v>0.4027819453613128</v>
+        <v>0.3466933152503658</v>
       </c>
       <c r="AL2">
-        <v>193.2</v>
+        <v>266.8</v>
       </c>
       <c r="AM2">
-        <v>193.2</v>
+        <v>266.8</v>
       </c>
       <c r="AN2">
-        <v>1.681223089196337</v>
+        <v>5.736613145614174</v>
       </c>
       <c r="AO2">
-        <v>21.64751552795031</v>
+        <v>3.899550224887556</v>
       </c>
       <c r="AP2">
-        <v>1.320219439162459</v>
+        <v>3.841651506762636</v>
       </c>
       <c r="AQ2">
-        <v>21.64751552795031</v>
+        <v>3.899550224887556</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00062</v>
+        <v>-0.09820000000000001</v>
       </c>
       <c r="E3">
-        <v>0.0313</v>
+        <v>0.0179</v>
       </c>
       <c r="F3">
-        <v>0.146</v>
+        <v>0.165</v>
       </c>
       <c r="G3">
-        <v>0.1441515893863818</v>
+        <v>0.1607987569776141</v>
       </c>
       <c r="H3">
-        <v>0.1441515893863818</v>
+        <v>0.1607987569776141</v>
       </c>
       <c r="I3">
-        <v>0.3086021664059503</v>
+        <v>0.1197444898428958</v>
       </c>
       <c r="J3">
-        <v>0.2520869274723158</v>
+        <v>0.1006980860497364</v>
       </c>
       <c r="K3">
-        <v>994.5</v>
+        <v>1140</v>
       </c>
       <c r="L3">
-        <v>0.07338183642749624</v>
+        <v>0.1312079185129769</v>
       </c>
       <c r="M3">
-        <v>600.4</v>
+        <v>626.8</v>
       </c>
       <c r="N3">
-        <v>0.07523809523809523</v>
+        <v>0.07028245293385511</v>
       </c>
       <c r="O3">
-        <v>0.6037204625439919</v>
+        <v>0.5498245614035088</v>
       </c>
       <c r="P3">
-        <v>589.5</v>
+        <v>626.8</v>
       </c>
       <c r="Q3">
-        <v>0.07387218045112783</v>
+        <v>0.07028245293385511</v>
       </c>
       <c r="R3">
-        <v>0.5927601809954751</v>
+        <v>0.5498245614035088</v>
       </c>
       <c r="S3">
-        <v>10.89999999999998</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.01815456362425046</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1651.7</v>
+        <v>2395.8</v>
       </c>
       <c r="V3">
-        <v>0.2069799498746867</v>
+        <v>0.2686386418936345</v>
       </c>
       <c r="W3">
-        <v>0.1054579387718312</v>
+        <v>0.1445306557127643</v>
       </c>
       <c r="X3">
-        <v>0.09753636610495922</v>
+        <v>0.09723750162383599</v>
       </c>
       <c r="Y3">
-        <v>0.007921572666872018</v>
+        <v>0.04729315408892834</v>
       </c>
       <c r="Z3">
-        <v>0.8649124710417319</v>
+        <v>0.6238153360137851</v>
       </c>
       <c r="AA3">
-        <v>0.2180331273573984</v>
+        <v>0.06281701038506134</v>
       </c>
       <c r="AB3">
-        <v>0.06974757697227713</v>
+        <v>0.07361927331655713</v>
       </c>
       <c r="AC3">
-        <v>0.1482855503851213</v>
+        <v>-0.01080226293149579</v>
       </c>
       <c r="AD3">
-        <v>7692.1</v>
+        <v>7252.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7692.1</v>
+        <v>7252.8</v>
       </c>
       <c r="AG3">
-        <v>6040.400000000001</v>
+        <v>4857</v>
       </c>
       <c r="AH3">
-        <v>0.4908148876028101</v>
+        <v>0.4485038123566115</v>
       </c>
       <c r="AI3">
-        <v>0.4620323874966963</v>
+        <v>0.4421010283262117</v>
       </c>
       <c r="AJ3">
-        <v>0.4308293629283045</v>
+        <v>0.3525876024478596</v>
       </c>
       <c r="AK3">
-        <v>0.4027819453613128</v>
+        <v>0.3466933152503658</v>
       </c>
       <c r="AL3">
-        <v>193.2</v>
+        <v>266.8</v>
       </c>
       <c r="AM3">
-        <v>193.2</v>
+        <v>266.8</v>
       </c>
       <c r="AN3">
-        <v>1.681223089196337</v>
+        <v>5.736613145614174</v>
       </c>
       <c r="AO3">
-        <v>21.64751552795031</v>
+        <v>3.899550224887556</v>
       </c>
       <c r="AP3">
-        <v>1.320219439162459</v>
+        <v>3.841651506762636</v>
       </c>
       <c r="AQ3">
-        <v>21.64751552795031</v>
+        <v>3.899550224887556</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/belgium/belgium_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_insurance_general.xlsx
@@ -648,10 +648,10 @@
         <v>0.1445306557127643</v>
       </c>
       <c r="X2">
-        <v>0.09723750162383599</v>
+        <v>0.09721347980345821</v>
       </c>
       <c r="Y2">
-        <v>0.04729315408892834</v>
+        <v>0.04731717590930612</v>
       </c>
       <c r="Z2">
         <v>0.6238153360137851</v>
@@ -660,10 +660,10 @@
         <v>0.06281701038506134</v>
       </c>
       <c r="AB2">
-        <v>0.07361927331655713</v>
+        <v>0.07360602537419852</v>
       </c>
       <c r="AC2">
-        <v>-0.01080226293149579</v>
+        <v>-0.01078901498913719</v>
       </c>
       <c r="AD2">
         <v>7252.8</v>
@@ -785,10 +785,10 @@
         <v>0.1445306557127643</v>
       </c>
       <c r="X3">
-        <v>0.09723750162383599</v>
+        <v>0.09721347980345821</v>
       </c>
       <c r="Y3">
-        <v>0.04729315408892834</v>
+        <v>0.04731717590930612</v>
       </c>
       <c r="Z3">
         <v>0.6238153360137851</v>
@@ -797,10 +797,10 @@
         <v>0.06281701038506134</v>
       </c>
       <c r="AB3">
-        <v>0.07361927331655713</v>
+        <v>0.07360602537419852</v>
       </c>
       <c r="AC3">
-        <v>-0.01080226293149579</v>
+        <v>-0.01078901498913719</v>
       </c>
       <c r="AD3">
         <v>7252.8</v>
